--- a/bom/BOM_SpatialForagingModule.xlsx
+++ b/bom/BOM_SpatialForagingModule.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2369487483669/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NeurotechHub\Programming\SpatialForagingPlatform-ProjectManager\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{A0CF5E18-DC51-7242-AF60-17C8F97E1C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4819A164-C41B-4E4D-A2E7-1419275F191A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC6A6B4-A89E-4F29-AF6C-EDAEE5F0DE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15680" yWindow="-32420" windowWidth="28040" windowHeight="17180" xr2:uid="{18EBE842-4B11-444E-A9D9-2818638CA39F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{18EBE842-4B11-444E-A9D9-2818638CA39F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hardware" sheetId="1" r:id="rId1"/>
+    <sheet name="Electronics" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="76">
   <si>
     <t>Item</t>
   </si>
@@ -204,6 +205,69 @@
   </si>
   <si>
     <t>(Cost/Pc)</t>
+  </si>
+  <si>
+    <t>Rpi kit</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0coOI5yY</t>
+  </si>
+  <si>
+    <t>Keyboard &amp; Mouse</t>
+  </si>
+  <si>
+    <t>https://a.co/d/04KC8G9F</t>
+  </si>
+  <si>
+    <t>Req. Items</t>
+  </si>
+  <si>
+    <t>Headers 8.5mm</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0ez4Hsjl</t>
+  </si>
+  <si>
+    <t>20mm standoff</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0bluxMO1</t>
+  </si>
+  <si>
+    <t>Ethernet cable</t>
+  </si>
+  <si>
+    <t>DC Power cable</t>
+  </si>
+  <si>
+    <t>28BYJ-48 Motors</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0dLrfPuQ</t>
+  </si>
+  <si>
+    <t>Power Supply</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0hV6RBvV</t>
+  </si>
+  <si>
+    <t>QT cables 200mm</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/4401/10824265</t>
+  </si>
+  <si>
+    <t>M2.5 screws</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0eXXSgv0</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>https://a.co/d/09T69M0k</t>
   </si>
 </sst>
 </file>
@@ -213,7 +277,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -242,6 +306,22 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -266,11 +346,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -279,9 +360,22 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -615,17 +709,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{421C52AF-D934-5E4D-A590-21C8983DA813}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="6"/>
-    <col min="7" max="7" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="59.33203125" customWidth="1"/>
-    <col min="11" max="11" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.796875" style="6"/>
+    <col min="7" max="7" width="13.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="59.296875" customWidth="1"/>
+    <col min="11" max="11" width="38.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -634,7 +728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +763,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -708,7 +802,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -747,7 +841,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -786,7 +880,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -825,7 +919,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -864,7 +958,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -903,7 +997,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -942,7 +1036,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -981,7 +1075,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1020,7 +1114,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1059,7 +1153,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -1095,7 +1189,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G16" s="5" t="s">
         <v>39</v>
       </c>
@@ -1104,7 +1198,7 @@
         <v>275.01</v>
       </c>
     </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G17" s="5" t="s">
         <v>40</v>
       </c>
@@ -1116,4 +1210,337 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8A2C5A5-03CA-4DB8-9D15-15879A9BBD02}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="2"/>
+    <col min="4" max="4" width="8.796875" style="13"/>
+    <col min="5" max="5" width="9.3984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.09765625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.796875" customWidth="1"/>
+    <col min="8" max="8" width="18.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1">
+        <v>16</v>
+      </c>
+      <c r="D1" s="12"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>219</v>
+      </c>
+      <c r="D4" s="13">
+        <v>1</v>
+      </c>
+      <c r="E4" s="16">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <f>C4*D4</f>
+        <v>219</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>39</v>
+      </c>
+      <c r="D5" s="13">
+        <v>1</v>
+      </c>
+      <c r="E5" s="16">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>39</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>39</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1</v>
+      </c>
+      <c r="E6" s="16">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <f>C6*D6</f>
+        <v>39</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>7</v>
+      </c>
+      <c r="D7" s="13">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <f>C7*D7</f>
+        <v>7</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <v>9</v>
+      </c>
+      <c r="D8" s="13">
+        <v>4</v>
+      </c>
+      <c r="E8" s="16">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>9</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13">
+        <v>4</v>
+      </c>
+      <c r="E9" s="16">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>6</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>25</v>
+      </c>
+      <c r="D10" s="13">
+        <v>1</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>25</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>5</v>
+      </c>
+      <c r="D11" s="13">
+        <f>B11*B$1</f>
+        <v>32</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <f>C11*D11</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>10</v>
+      </c>
+      <c r="D12" s="13">
+        <f>B12*B$1</f>
+        <v>32</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <f>C12*D12</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>6</v>
+      </c>
+      <c r="D13" s="13">
+        <f>B13*B$1</f>
+        <v>32</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <f>C13*D13</f>
+        <v>192</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>6</v>
+      </c>
+      <c r="D14" s="13">
+        <f>B14*B$1</f>
+        <v>48</v>
+      </c>
+      <c r="E14" s="16">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <f>C14*D14</f>
+        <v>288</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G4" r:id="rId1" xr:uid="{A29BB3D4-2B55-493A-9A14-782DA745B2D2}"/>
+    <hyperlink ref="G6" r:id="rId2" xr:uid="{140BE8E7-9276-4E09-AA0C-5C2546A0C34D}"/>
+    <hyperlink ref="G7" r:id="rId3" xr:uid="{FD07F96D-6BED-41D9-98C4-4ACB0221779F}"/>
+    <hyperlink ref="G8" r:id="rId4" xr:uid="{4C1A4761-F7F8-4485-8ABB-6B2CE086DE14}"/>
+    <hyperlink ref="G13" r:id="rId5" xr:uid="{DBF367EE-CE06-452A-92D9-783D2D7312DA}"/>
+    <hyperlink ref="G10" r:id="rId6" xr:uid="{2505CAD8-C26D-45F8-A8AF-75EEFF397939}"/>
+    <hyperlink ref="G14" r:id="rId7" xr:uid="{58CB83C6-4509-439E-92CF-04F3514DCA2D}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{DB4142FC-9666-4E1D-861D-07218E12769C}"/>
+    <hyperlink ref="G5" r:id="rId9" xr:uid="{42F1FCD5-B2C2-4FB6-851B-B5307ED3137A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/bom/BOM_SpatialForagingModule.xlsx
+++ b/bom/BOM_SpatialForagingModule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NeurotechHub\Programming\SpatialForagingPlatform-ProjectManager\bom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mattgaidica/Documents/Software/SpatialForagingPlatform/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC6A6B4-A89E-4F29-AF6C-EDAEE5F0DE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDFE3EA-9BF0-5B4F-8556-718FCB335CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{18EBE842-4B11-444E-A9D9-2818638CA39F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{18EBE842-4B11-444E-A9D9-2818638CA39F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hardware" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="75">
   <si>
     <t>Item</t>
   </si>
@@ -108,12 +108,6 @@
     <t>91292A005</t>
   </si>
   <si>
-    <t>92095A287</t>
-  </si>
-  <si>
-    <t>https://www.mcmaster.com/92095A287/</t>
-  </si>
-  <si>
     <t>94500A265</t>
   </si>
   <si>
@@ -165,9 +159,6 @@
     <t>total/module</t>
   </si>
   <si>
-    <t>M3 × 3 button head</t>
-  </si>
-  <si>
     <t>M2 × 5 countersunk</t>
   </si>
   <si>
@@ -268,6 +259,12 @@
   </si>
   <si>
     <t>https://a.co/d/09T69M0k</t>
+  </si>
+  <si>
+    <t>M4 × 3 button head screw</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0iulvyI3</t>
   </si>
 </sst>
 </file>
@@ -351,7 +348,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -366,12 +363,9 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -709,17 +703,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{421C52AF-D934-5E4D-A590-21C8983DA813}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.796875" style="6"/>
-    <col min="7" max="7" width="13.296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="59.296875" customWidth="1"/>
-    <col min="11" max="11" width="38.796875" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="6"/>
+    <col min="7" max="7" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="59.33203125" customWidth="1"/>
+    <col min="11" max="11" width="38.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -728,7 +722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -742,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>4</v>
@@ -754,7 +748,7 @@
         <v>7</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>5</v>
@@ -763,12 +757,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -796,15 +790,15 @@
         <v>0.15421874999999999</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -835,13 +829,13 @@
         <v>0.20250000000000001</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -874,18 +868,15 @@
         <v>0.26104166666666667</v>
       </c>
       <c r="J6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -902,24 +893,24 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>12.49</v>
+        <v>7.38</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="2"/>
-        <v>12.49</v>
+        <v>7.38</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="3"/>
-        <v>0.19515625</v>
+        <v>0.1153125</v>
       </c>
       <c r="J7" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -952,13 +943,13 @@
         <v>7.7708333333333338E-2</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -991,13 +982,13 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="J9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1030,13 +1021,13 @@
         <v>0.1027734375</v>
       </c>
       <c r="J10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1069,18 +1060,18 @@
         <v>0.32624999999999998</v>
       </c>
       <c r="J11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -1108,18 +1099,18 @@
         <v>0.875</v>
       </c>
       <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
-      <c r="K12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1147,15 +1138,15 @@
         <v>4.7</v>
       </c>
       <c r="J13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -1183,28 +1174,28 @@
         <v>0.29375000000000001</v>
       </c>
       <c r="J14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G16" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H16" s="4">
         <f>SUM(H4:H14)</f>
-        <v>275.01</v>
-      </c>
-    </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.3">
+        <v>269.89999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G17" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H17" s="4">
         <f>H16/C1</f>
-        <v>17.188124999999999</v>
+        <v>16.868749999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1215,37 +1206,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8A2C5A5-03CA-4DB8-9D15-15879A9BBD02}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.796875" style="2"/>
-    <col min="4" max="4" width="8.796875" style="13"/>
-    <col min="5" max="5" width="9.3984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.09765625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.796875" customWidth="1"/>
-    <col min="8" max="8" width="18.59765625" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2"/>
+    <col min="4" max="4" width="8.83203125" style="12"/>
+    <col min="5" max="5" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="1">
         <v>16</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D1" s="1"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2"/>
       <c r="B2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="16"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
@@ -1255,11 +1246,11 @@
       <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>59</v>
+      <c r="D3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>7</v>
@@ -1271,9 +1262,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1281,10 +1272,10 @@
       <c r="C4" s="2">
         <v>219</v>
       </c>
-      <c r="D4" s="13">
-        <v>1</v>
-      </c>
-      <c r="E4" s="16">
+      <c r="D4" s="12">
+        <v>1</v>
+      </c>
+      <c r="E4" s="13">
         <v>0</v>
       </c>
       <c r="F4" s="2">
@@ -1292,12 +1283,12 @@
         <v>219</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1305,22 +1296,22 @@
       <c r="C5" s="2">
         <v>39</v>
       </c>
-      <c r="D5" s="13">
-        <v>1</v>
-      </c>
-      <c r="E5" s="16">
+      <c r="D5" s="12">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13">
         <v>1</v>
       </c>
       <c r="F5" s="2">
         <v>39</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1328,10 +1319,10 @@
       <c r="C6" s="2">
         <v>39</v>
       </c>
-      <c r="D6" s="13">
-        <v>1</v>
-      </c>
-      <c r="E6" s="16">
+      <c r="D6" s="12">
+        <v>1</v>
+      </c>
+      <c r="E6" s="13">
         <v>1</v>
       </c>
       <c r="F6" s="2">
@@ -1339,12 +1330,12 @@
         <v>39</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1352,10 +1343,10 @@
       <c r="C7" s="2">
         <v>7</v>
       </c>
-      <c r="D7" s="13">
-        <v>1</v>
-      </c>
-      <c r="E7" s="16">
+      <c r="D7" s="12">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13">
         <v>0</v>
       </c>
       <c r="F7" s="2">
@@ -1363,12 +1354,12 @@
         <v>7</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1376,22 +1367,22 @@
       <c r="C8" s="2">
         <v>9</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>4</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="13">
         <v>0</v>
       </c>
       <c r="F8" s="2">
         <v>9</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -1399,22 +1390,22 @@
       <c r="C9" s="2">
         <v>6</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>4</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="13">
         <v>1</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1422,22 +1413,22 @@
       <c r="C10" s="2">
         <v>25</v>
       </c>
-      <c r="D10" s="13">
-        <v>1</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="12">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13">
         <v>0</v>
       </c>
       <c r="F10" s="2">
         <v>25</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1445,11 +1436,11 @@
       <c r="C11" s="2">
         <v>5</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f>B11*B$1</f>
         <v>32</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="13">
         <v>0</v>
       </c>
       <c r="F11" s="2">
@@ -1457,9 +1448,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -1467,11 +1458,11 @@
       <c r="C12" s="2">
         <v>10</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <f>B12*B$1</f>
         <v>32</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="13">
         <v>0</v>
       </c>
       <c r="F12" s="2">
@@ -1479,9 +1470,9 @@
         <v>320</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -1489,11 +1480,11 @@
       <c r="C13" s="2">
         <v>6</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f>B13*B$1</f>
         <v>32</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="13">
         <v>0</v>
       </c>
       <c r="F13" s="2">
@@ -1501,12 +1492,12 @@
         <v>192</v>
       </c>
       <c r="G13" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>70</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -1514,11 +1505,11 @@
       <c r="C14" s="2">
         <v>6</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <f>B14*B$1</f>
         <v>48</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="13">
         <v>0</v>
       </c>
       <c r="F14" s="2">
@@ -1526,7 +1517,7 @@
         <v>288</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/bom/BOM_SpatialForagingModule.xlsx
+++ b/bom/BOM_SpatialForagingModule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mattgaidica/Documents/Software/SpatialForagingPlatform/bom/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gaidica/Documents/Software/SpatialForagingPlatform-ProjectManager/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDFE3EA-9BF0-5B4F-8556-718FCB335CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED4AEA2-6BCB-9249-8A6B-02E06271EC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{18EBE842-4B11-444E-A9D9-2818638CA39F}"/>
   </bookViews>
@@ -264,7 +264,7 @@
     <t>M4 × 3 button head screw</t>
   </si>
   <si>
-    <t>https://a.co/d/0iulvyI3</t>
+    <t>https://a.co/d/08jMKRfI</t>
   </si>
 </sst>
 </file>
@@ -879,7 +879,7 @@
         <v>73</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -890,18 +890,18 @@
       </c>
       <c r="F7" s="6">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2">
-        <v>7.38</v>
+        <v>5.72</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="2"/>
-        <v>7.38</v>
+        <v>11.44</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="3"/>
-        <v>0.1153125</v>
+        <v>0.17874999999999999</v>
       </c>
       <c r="J7" t="s">
         <v>74</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H16" s="4">
         <f>SUM(H4:H14)</f>
-        <v>269.89999999999998</v>
+        <v>273.95999999999998</v>
       </c>
     </row>
     <row r="17" spans="7:8" x14ac:dyDescent="0.2">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H17" s="4">
         <f>H16/C1</f>
-        <v>16.868749999999999</v>
+        <v>17.122499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/bom/BOM_SpatialForagingModule.xlsx
+++ b/bom/BOM_SpatialForagingModule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gaidica/Documents/Software/SpatialForagingPlatform-ProjectManager/bom/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mattgaidica/Documents/Software/SpatialForagingPlatform/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED4AEA2-6BCB-9249-8A6B-02E06271EC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5371B4B6-A8E3-A240-8E89-E2ED1B89B8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{18EBE842-4B11-444E-A9D9-2818638CA39F}"/>
+    <workbookView xWindow="3660" yWindow="1880" windowWidth="26580" windowHeight="17760" xr2:uid="{18EBE842-4B11-444E-A9D9-2818638CA39F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hardware" sheetId="1" r:id="rId1"/>
@@ -105,9 +105,6 @@
     <t>Part Number</t>
   </si>
   <si>
-    <t>91292A005</t>
-  </si>
-  <si>
     <t>94500A265</t>
   </si>
   <si>
@@ -265,6 +262,9 @@
   </si>
   <si>
     <t>https://a.co/d/08jMKRfI</t>
+  </si>
+  <si>
+    <t>92125A051</t>
   </si>
 </sst>
 </file>
@@ -736,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>4</v>
@@ -748,7 +748,7 @@
         <v>7</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>5</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -790,18 +790,18 @@
         <v>0.15421874999999999</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -829,10 +829,10 @@
         <v>0.20250000000000001</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -868,15 +868,15 @@
         <v>0.26104166666666667</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -904,10 +904,10 @@
         <v>0.17874999999999999</v>
       </c>
       <c r="J7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -943,10 +943,10 @@
         <v>7.7708333333333338E-2</v>
       </c>
       <c r="J8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -982,10 +982,10 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="J9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -1021,10 +1021,10 @@
         <v>0.1027734375</v>
       </c>
       <c r="J10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -1060,10 +1060,10 @@
         <v>0.32624999999999998</v>
       </c>
       <c r="J11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1071,7 +1071,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -1099,18 +1099,18 @@
         <v>0.875</v>
       </c>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1138,15 +1138,15 @@
         <v>4.7</v>
       </c>
       <c r="J13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -1174,15 +1174,15 @@
         <v>0.29375000000000001</v>
       </c>
       <c r="J14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G16" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H16" s="4">
         <f>SUM(H4:H14)</f>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="17" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H17" s="4">
         <f>H16/C1</f>
@@ -1247,10 +1247,10 @@
         <v>6</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>7</v>
@@ -1264,7 +1264,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1283,12 +1283,12 @@
         <v>219</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1306,12 +1306,12 @@
         <v>39</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1330,12 +1330,12 @@
         <v>39</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1354,12 +1354,12 @@
         <v>7</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1377,12 +1377,12 @@
         <v>9</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -1400,12 +1400,12 @@
         <v>6</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1423,12 +1423,12 @@
         <v>25</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -1472,7 +1472,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -1492,12 +1492,12 @@
         <v>192</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -1517,7 +1517,7 @@
         <v>288</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
